--- a/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 2.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 2.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="Calificaciones" sheetId="1" r:id="rId1"/>
     <sheet name="Estandar" sheetId="2" r:id="rId2"/>
+    <sheet name="Cronograma" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7881,4 +7882,203 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin_clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 2.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2425-3/Partic. Emergente 2425-3 Secc. 2.xlsx
@@ -7923,7 +7923,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -7934,7 +7934,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -7972,7 +7972,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -7983,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -7994,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -8021,7 +8021,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -8048,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
